--- a/src/fixtures/sample/gstr2b-2025-10.xlsx
+++ b/src/fixtures/sample/gstr2b-2025-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,25 +470,25 @@
         <v>Mahesh Steel Traders</v>
       </c>
       <c r="C6" t="str">
-        <v>S01/2025/013</v>
+        <v>S01/2025/011</v>
       </c>
       <c r="D6" t="str">
-        <v>10/10/2025</v>
+        <v>25/10/2025</v>
       </c>
       <c r="E6">
-        <v>580560</v>
+        <v>562860</v>
       </c>
       <c r="F6">
-        <v>492000</v>
+        <v>477000</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>44280</v>
+        <v>42930</v>
       </c>
       <c r="I6">
-        <v>44280</v>
+        <v>42930</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>2025-11</v>
       </c>
       <c r="L6" t="str">
-        <v>11/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -511,31 +511,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>24AAGCA1188M1ZI</v>
+        <v>27AAPFM4821K1ZV</v>
       </c>
       <c r="B7" t="str">
-        <v>Anand Polymers</v>
+        <v>Mahesh Steel Traders</v>
       </c>
       <c r="C7" t="str">
-        <v>S05/2025/011</v>
+        <v>S01/2025/013</v>
       </c>
       <c r="D7" t="str">
-        <v>13/10/2025</v>
+        <v>15/10/2025</v>
       </c>
       <c r="E7">
-        <v>364620</v>
+        <v>580560</v>
       </c>
       <c r="F7">
-        <v>309000</v>
+        <v>492000</v>
       </c>
       <c r="G7">
-        <v>55620</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>44280</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>44280</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>2025-11</v>
       </c>
       <c r="L7" t="str">
-        <v>12/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -564,19 +564,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C8" t="str">
-        <v>S05/2025/012</v>
+        <v>S05/2025/011</v>
       </c>
       <c r="D8" t="str">
-        <v>16/10/2025</v>
+        <v>02/10/2025</v>
       </c>
       <c r="E8">
-        <v>351640</v>
+        <v>363440</v>
       </c>
       <c r="F8">
-        <v>298000</v>
+        <v>308000</v>
       </c>
       <c r="G8">
-        <v>53640</v>
+        <v>55440</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>2025-11</v>
       </c>
       <c r="L8" t="str">
-        <v>11/11/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -611,19 +611,19 @@
         <v>Anand Polymers</v>
       </c>
       <c r="C9" t="str">
-        <v>S05/2025/013</v>
+        <v>S05/2025/012</v>
       </c>
       <c r="D9" t="str">
-        <v>13/10/2025</v>
+        <v>14/10/2025</v>
       </c>
       <c r="E9">
-        <v>363440</v>
+        <v>361080</v>
       </c>
       <c r="F9">
-        <v>308000</v>
+        <v>306000</v>
       </c>
       <c r="G9">
-        <v>55440</v>
+        <v>55080</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>2025-11</v>
       </c>
       <c r="L9" t="str">
-        <v>14/11/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -652,31 +652,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>27AABFS9034J1ZY</v>
+        <v>24AAGCA1188M1ZI</v>
       </c>
       <c r="B10" t="str">
-        <v>Surya Electricals</v>
+        <v>Anand Polymers</v>
       </c>
       <c r="C10" t="str">
-        <v>SE 11</v>
+        <v>S05/2025/013</v>
       </c>
       <c r="D10" t="str">
-        <v>07/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="E10">
-        <v>159300</v>
+        <v>377600</v>
       </c>
       <c r="F10">
-        <v>135000</v>
+        <v>320000</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="H10">
-        <v>12150</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>12150</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>2025-11</v>
       </c>
       <c r="L10" t="str">
-        <v>14/11/2025</v>
+        <v>15/11/2025</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -708,22 +708,22 @@
         <v>SE 11</v>
       </c>
       <c r="D11" t="str">
-        <v>10/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="E11">
-        <v>159300</v>
+        <v>168740</v>
       </c>
       <c r="F11">
-        <v>135000</v>
+        <v>143000</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>12150</v>
+        <v>12870</v>
       </c>
       <c r="I11">
-        <v>12150</v>
+        <v>12870</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>2025-11</v>
       </c>
       <c r="L11" t="str">
-        <v>13/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -746,31 +746,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>24AAECR8890P1ZI</v>
+        <v>27AABFS9034J1ZY</v>
       </c>
       <c r="B12" t="str">
-        <v>Ratna Chemicals</v>
+        <v>Surya Electricals</v>
       </c>
       <c r="C12" t="str">
-        <v>S08/2025/011</v>
+        <v>SE 11</v>
       </c>
       <c r="D12" t="str">
-        <v>13/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="E12">
-        <v>205320</v>
+        <v>179360</v>
       </c>
       <c r="F12">
-        <v>174000</v>
+        <v>152000</v>
       </c>
       <c r="G12">
-        <v>31320</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>13680</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>13680</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>2025-11</v>
       </c>
       <c r="L12" t="str">
-        <v>15/11/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -799,19 +799,19 @@
         <v>Ratna Chemicals</v>
       </c>
       <c r="C13" t="str">
-        <v>S08/2025/012</v>
+        <v>S08/2025/011</v>
       </c>
       <c r="D13" t="str">
-        <v>12/10/2025</v>
+        <v>03/10/2025</v>
       </c>
       <c r="E13">
-        <v>221840</v>
+        <v>217120</v>
       </c>
       <c r="F13">
-        <v>188000</v>
+        <v>184000</v>
       </c>
       <c r="G13">
-        <v>33840</v>
+        <v>33120</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>2025-11</v>
       </c>
       <c r="L13" t="str">
-        <v>09/11/2025</v>
+        <v>15/11/2025</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -840,31 +840,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>27AAACM6543N1Z3</v>
+        <v>24AAECR8890P1ZI</v>
       </c>
       <c r="B14" t="str">
-        <v>Metro Motors</v>
+        <v>Ratna Chemicals</v>
       </c>
       <c r="C14" t="str">
-        <v>S09/2025/011</v>
+        <v>S08/2025/012</v>
       </c>
       <c r="D14" t="str">
-        <v>03/10/2025</v>
+        <v>17/10/2025</v>
       </c>
       <c r="E14">
-        <v>1057280</v>
+        <v>220660</v>
       </c>
       <c r="F14">
-        <v>896000</v>
+        <v>187000</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>33660</v>
       </c>
       <c r="H14">
-        <v>80640</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>80640</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>2025-11</v>
       </c>
       <c r="L14" t="str">
-        <v>15/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="N14" t="str">
-        <v>ITC unavailable - blocked credit</v>
+        <v/>
       </c>
       <c r="O14" t="str">
         <v>N</v>
@@ -887,31 +887,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>27AAFCV4412Q2ZU</v>
+        <v>27AAACM6543N1Z3</v>
       </c>
       <c r="B15" t="str">
-        <v>Vindhya Alloys</v>
+        <v>Metro Motors</v>
       </c>
       <c r="C15" t="str">
-        <v>S10/2025/011</v>
+        <v>S09/2025/011</v>
       </c>
       <c r="D15" t="str">
-        <v>18/10/2025</v>
+        <v>19/10/2025</v>
       </c>
       <c r="E15">
-        <v>313880</v>
+        <v>1045480</v>
       </c>
       <c r="F15">
-        <v>266000</v>
+        <v>886000</v>
       </c>
       <c r="G15">
-        <v>47880</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>79740</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>79740</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -920,13 +920,13 @@
         <v>2025-11</v>
       </c>
       <c r="L15" t="str">
-        <v>16/11/2025</v>
+        <v>15/11/2025</v>
       </c>
       <c r="M15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>ITC unavailable - blocked credit</v>
       </c>
       <c r="O15" t="str">
         <v>N</v>
@@ -940,19 +940,19 @@
         <v>Vindhya Alloys</v>
       </c>
       <c r="C16" t="str">
-        <v>S10/2025/012</v>
+        <v>S10/2025/011</v>
       </c>
       <c r="D16" t="str">
-        <v>10/10/2025</v>
+        <v>13/10/2025</v>
       </c>
       <c r="E16">
-        <v>323320</v>
+        <v>319780</v>
       </c>
       <c r="F16">
-        <v>274000</v>
+        <v>271000</v>
       </c>
       <c r="G16">
-        <v>49320</v>
+        <v>48780</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>2025-11</v>
       </c>
       <c r="L16" t="str">
-        <v>11/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="M16" t="str">
         <v>Yes</v>
@@ -981,31 +981,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27AAFCB2210G1Z8</v>
+        <v>27AAFCV4412Q2ZU</v>
       </c>
       <c r="B17" t="str">
-        <v>Bharat Office Supplies</v>
+        <v>Vindhya Alloys</v>
       </c>
       <c r="C17" t="str">
-        <v>S12/2025/002</v>
+        <v>S10/2025/012</v>
       </c>
       <c r="D17" t="str">
-        <v>18/09/2025</v>
+        <v>21/10/2025</v>
       </c>
       <c r="E17">
-        <v>189980</v>
+        <v>313880</v>
       </c>
       <c r="F17">
-        <v>161000</v>
+        <v>266000</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>47880</v>
       </c>
       <c r="H17">
-        <v>14490</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>14490</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>2025-11</v>
       </c>
       <c r="L17" t="str">
-        <v>16/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M17" t="str">
         <v>Yes</v>
@@ -1037,22 +1037,22 @@
         <v>S12/2025/011</v>
       </c>
       <c r="D18" t="str">
-        <v>10/10/2025</v>
+        <v>26/10/2025</v>
       </c>
       <c r="E18">
-        <v>193520</v>
+        <v>197060</v>
       </c>
       <c r="F18">
-        <v>164000</v>
+        <v>167000</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>14760</v>
+        <v>15030</v>
       </c>
       <c r="I18">
-        <v>14760</v>
+        <v>15030</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>2025-11</v>
       </c>
       <c r="L18" t="str">
-        <v>09/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M18" t="str">
         <v>Yes</v>
@@ -1084,22 +1084,22 @@
         <v>S12/2025/012</v>
       </c>
       <c r="D19" t="str">
-        <v>13/10/2025</v>
+        <v>04/10/2025</v>
       </c>
       <c r="E19">
-        <v>204140</v>
+        <v>186440</v>
       </c>
       <c r="F19">
-        <v>173000</v>
+        <v>158000</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>15570</v>
+        <v>14220</v>
       </c>
       <c r="I19">
-        <v>15570</v>
+        <v>14220</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>2025-11</v>
       </c>
       <c r="L19" t="str">
-        <v>08/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="M19" t="str">
         <v>Yes</v>
@@ -1131,22 +1131,22 @@
         <v>S13/2025/011</v>
       </c>
       <c r="D20" t="str">
-        <v>04/10/2025</v>
+        <v>14/10/2025</v>
       </c>
       <c r="E20">
-        <v>82600</v>
+        <v>97940</v>
       </c>
       <c r="F20">
-        <v>70000</v>
+        <v>83000</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>6300</v>
+        <v>7470</v>
       </c>
       <c r="I20">
-        <v>6300</v>
+        <v>7470</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>2025-11</v>
       </c>
       <c r="L20" t="str">
-        <v>10/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M20" t="str">
         <v>Yes</v>
@@ -1178,16 +1178,16 @@
         <v>S14/2025/011</v>
       </c>
       <c r="D21" t="str">
-        <v>07/10/2025</v>
+        <v>13/10/2025</v>
       </c>
       <c r="E21">
-        <v>159300</v>
+        <v>135700</v>
       </c>
       <c r="F21">
-        <v>135000</v>
+        <v>115000</v>
       </c>
       <c r="G21">
-        <v>24300</v>
+        <v>20700</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         <v>2025-11</v>
       </c>
       <c r="L21" t="str">
-        <v>09/11/2025</v>
+        <v>11/11/2025</v>
       </c>
       <c r="M21" t="str">
         <v>Yes</v>
@@ -1225,16 +1225,16 @@
         <v>S15/2025/011</v>
       </c>
       <c r="D22" t="str">
-        <v>12/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="E22">
-        <v>53100</v>
+        <v>48380</v>
       </c>
       <c r="F22">
-        <v>45000</v>
+        <v>41000</v>
       </c>
       <c r="G22">
-        <v>8100</v>
+        <v>7380</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>2025-11</v>
       </c>
       <c r="L22" t="str">
-        <v>09/11/2025</v>
+        <v>14/11/2025</v>
       </c>
       <c r="M22" t="str">
         <v>Yes</v>
@@ -1275,13 +1275,13 @@
         <v>19/10/2025</v>
       </c>
       <c r="E23">
-        <v>43660</v>
+        <v>50740</v>
       </c>
       <c r="F23">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="G23">
-        <v>6660</v>
+        <v>7740</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2025-11</v>
       </c>
       <c r="L23" t="str">
-        <v>14/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M23" t="str">
         <v>Yes</v>
@@ -1319,16 +1319,16 @@
         <v>S15/2025/013</v>
       </c>
       <c r="D24" t="str">
-        <v>03/10/2025</v>
+        <v>21/10/2025</v>
       </c>
       <c r="E24">
-        <v>35400</v>
+        <v>47200</v>
       </c>
       <c r="F24">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="G24">
-        <v>5400</v>
+        <v>7200</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>2025-11</v>
       </c>
       <c r="L24" t="str">
-        <v>12/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="M24" t="str">
         <v>Yes</v>
@@ -1366,16 +1366,16 @@
         <v>S16/2025/011</v>
       </c>
       <c r="D25" t="str">
-        <v>21/10/2025</v>
+        <v>15/10/2025</v>
       </c>
       <c r="E25">
-        <v>73160</v>
+        <v>68440</v>
       </c>
       <c r="F25">
-        <v>62000</v>
+        <v>58000</v>
       </c>
       <c r="G25">
-        <v>11160</v>
+        <v>10440</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>2025-11</v>
       </c>
       <c r="L25" t="str">
-        <v>09/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M25" t="str">
         <v>Yes</v>
@@ -1413,16 +1413,16 @@
         <v>S16/2025/012</v>
       </c>
       <c r="D26" t="str">
-        <v>10/10/2025</v>
+        <v>18/10/2025</v>
       </c>
       <c r="E26">
-        <v>80240</v>
+        <v>57820</v>
       </c>
       <c r="F26">
-        <v>68000</v>
+        <v>49000</v>
       </c>
       <c r="G26">
-        <v>12240</v>
+        <v>8820</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>2025-11</v>
       </c>
       <c r="L26" t="str">
-        <v>10/11/2025</v>
+        <v>15/11/2025</v>
       </c>
       <c r="M26" t="str">
         <v>Yes</v>
@@ -1460,16 +1460,16 @@
         <v>S17/2025/011</v>
       </c>
       <c r="D27" t="str">
-        <v>15/10/2025</v>
+        <v>16/10/2025</v>
       </c>
       <c r="E27">
-        <v>48380</v>
+        <v>62540</v>
       </c>
       <c r="F27">
-        <v>41000</v>
+        <v>53000</v>
       </c>
       <c r="G27">
-        <v>7380</v>
+        <v>9540</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>S18/2025/011</v>
       </c>
       <c r="D28" t="str">
-        <v>23/10/2025</v>
+        <v>08/10/2025</v>
       </c>
       <c r="E28">
         <v>173460</v>
@@ -1531,7 +1531,7 @@
         <v>2025-11</v>
       </c>
       <c r="L28" t="str">
-        <v>11/11/2025</v>
+        <v>16/11/2025</v>
       </c>
       <c r="M28" t="str">
         <v>Yes</v>
@@ -1554,22 +1554,22 @@
         <v>S18/2025/012</v>
       </c>
       <c r="D29" t="str">
-        <v>04/10/2025</v>
+        <v>17/10/2025</v>
       </c>
       <c r="E29">
-        <v>151040</v>
+        <v>172280</v>
       </c>
       <c r="F29">
-        <v>128000</v>
+        <v>146000</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>11520</v>
+        <v>13140</v>
       </c>
       <c r="I29">
-        <v>11520</v>
+        <v>13140</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1601,22 +1601,22 @@
         <v>S18/2025/013</v>
       </c>
       <c r="D30" t="str">
-        <v>03/10/2025</v>
+        <v>24/10/2025</v>
       </c>
       <c r="E30">
-        <v>164020</v>
+        <v>162840</v>
       </c>
       <c r="F30">
-        <v>139000</v>
+        <v>138000</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>12510</v>
+        <v>12420</v>
       </c>
       <c r="I30">
-        <v>12510</v>
+        <v>12420</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>2025-11</v>
       </c>
       <c r="L30" t="str">
-        <v>14/11/2025</v>
+        <v>08/11/2025</v>
       </c>
       <c r="M30" t="str">
         <v>Yes</v>
@@ -1648,7 +1648,7 @@
         <v>S19/2025/011</v>
       </c>
       <c r="D31" t="str">
-        <v>10/10/2025</v>
+        <v>04/10/2025</v>
       </c>
       <c r="E31">
         <v>112100</v>
@@ -1672,7 +1672,7 @@
         <v>2025-11</v>
       </c>
       <c r="L31" t="str">
-        <v>15/11/2025</v>
+        <v>10/11/2025</v>
       </c>
       <c r="M31" t="str">
         <v>Yes</v>
@@ -1686,31 +1686,31 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>33AABFS2234V1ZT</v>
+        <v>27AAFCA8801X1ZT</v>
       </c>
       <c r="B32" t="str">
-        <v>Sundar Printing Works</v>
+        <v>Ashoka Civil Works</v>
       </c>
       <c r="C32" t="str">
-        <v>S19/2025/012</v>
+        <v>S20/2025/011</v>
       </c>
       <c r="D32" t="str">
-        <v>21/10/2025</v>
+        <v>07/10/2025</v>
       </c>
       <c r="E32">
-        <v>90860</v>
+        <v>135700</v>
       </c>
       <c r="F32">
-        <v>77000</v>
+        <v>115000</v>
       </c>
       <c r="G32">
-        <v>13860</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>10350</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>10350</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1719,7 +1719,7 @@
         <v>2025-11</v>
       </c>
       <c r="L32" t="str">
-        <v>11/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M32" t="str">
         <v>Yes</v>
@@ -1739,25 +1739,25 @@
         <v>Ashoka Civil Works</v>
       </c>
       <c r="C33" t="str">
-        <v>S20/2025/011</v>
+        <v>S20/2025/012</v>
       </c>
       <c r="D33" t="str">
-        <v>18/10/2025</v>
+        <v>21/10/2025</v>
       </c>
       <c r="E33">
-        <v>142780</v>
+        <v>132160</v>
       </c>
       <c r="F33">
-        <v>121000</v>
+        <v>112000</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>10890</v>
+        <v>10080</v>
       </c>
       <c r="I33">
-        <v>10890</v>
+        <v>10080</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1780,31 +1780,31 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>27AAFCA8801X1ZT</v>
+        <v>29AADCN3345Z1ZD</v>
       </c>
       <c r="B34" t="str">
-        <v>Ashoka Civil Works</v>
+        <v>Nova Instruments</v>
       </c>
       <c r="C34" t="str">
-        <v>S20/2025/012</v>
+        <v>S21/2025/002</v>
       </c>
       <c r="D34" t="str">
-        <v>17/10/2025</v>
+        <v>04/09/2025</v>
       </c>
       <c r="E34">
-        <v>135700</v>
+        <v>208860</v>
       </c>
       <c r="F34">
-        <v>115000</v>
+        <v>177000</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>31860</v>
       </c>
       <c r="H34">
-        <v>10350</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>10350</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1836,16 +1836,16 @@
         <v>S21/2025/011</v>
       </c>
       <c r="D35" t="str">
-        <v>15/10/2025</v>
+        <v>12/10/2025</v>
       </c>
       <c r="E35">
-        <v>185260</v>
+        <v>182900</v>
       </c>
       <c r="F35">
-        <v>157000</v>
+        <v>155000</v>
       </c>
       <c r="G35">
-        <v>28260</v>
+        <v>27900</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>2025-11</v>
       </c>
       <c r="L35" t="str">
-        <v>08/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M35" t="str">
         <v>Yes</v>
@@ -1883,16 +1883,16 @@
         <v>S21/2025/012</v>
       </c>
       <c r="D36" t="str">
-        <v>17/10/2025</v>
+        <v>25/10/2025</v>
       </c>
       <c r="E36">
-        <v>197060</v>
+        <v>207680</v>
       </c>
       <c r="F36">
-        <v>167000</v>
+        <v>176000</v>
       </c>
       <c r="G36">
-        <v>30060</v>
+        <v>31680</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>2025-11</v>
       </c>
       <c r="L36" t="str">
-        <v>11/11/2025</v>
+        <v>15/11/2025</v>
       </c>
       <c r="M36" t="str">
         <v>Yes</v>
@@ -1930,16 +1930,16 @@
         <v>S21/2025/013</v>
       </c>
       <c r="D37" t="str">
-        <v>04/10/2025</v>
+        <v>03/10/2025</v>
       </c>
       <c r="E37">
-        <v>205320</v>
+        <v>207680</v>
       </c>
       <c r="F37">
-        <v>174000</v>
+        <v>176000</v>
       </c>
       <c r="G37">
-        <v>31320</v>
+        <v>31680</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>2025-11</v>
       </c>
       <c r="L37" t="str">
-        <v>10/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M37" t="str">
         <v>Yes</v>
@@ -1977,22 +1977,22 @@
         <v>S22/2025/011</v>
       </c>
       <c r="D38" t="str">
-        <v>09/10/2025</v>
+        <v>02/10/2025</v>
       </c>
       <c r="E38">
-        <v>217120</v>
+        <v>214760</v>
       </c>
       <c r="F38">
-        <v>184000</v>
+        <v>182000</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>16560</v>
+        <v>16380</v>
       </c>
       <c r="I38">
-        <v>16560</v>
+        <v>16380</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>2025-11</v>
       </c>
       <c r="L38" t="str">
-        <v>15/11/2025</v>
+        <v>12/11/2025</v>
       </c>
       <c r="M38" t="str">
         <v>Yes</v>
@@ -2021,19 +2021,19 @@
         <v>Coral Adhesives</v>
       </c>
       <c r="C39" t="str">
-        <v>S23/2025/001</v>
+        <v>S23/2025/011</v>
       </c>
       <c r="D39" t="str">
-        <v>18/09/2025</v>
+        <v>09/10/2025</v>
       </c>
       <c r="E39">
-        <v>205320</v>
+        <v>189980</v>
       </c>
       <c r="F39">
-        <v>174000</v>
+        <v>161000</v>
       </c>
       <c r="G39">
-        <v>31320</v>
+        <v>28980</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>2025-11</v>
       </c>
       <c r="L39" t="str">
-        <v>14/11/2025</v>
+        <v>08/11/2025</v>
       </c>
       <c r="M39" t="str">
         <v>Yes</v>
@@ -2062,25 +2062,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>24AAECC7789B1ZM</v>
+        <v>09AAJFY5523C1Z3</v>
       </c>
       <c r="B40" t="str">
-        <v>Coral Adhesives</v>
+        <v>Yamuna Agro Products</v>
       </c>
       <c r="C40" t="str">
-        <v>S23/2025/011</v>
+        <v>S24/2025/011</v>
       </c>
       <c r="D40" t="str">
-        <v>04/10/2025</v>
+        <v>06/10/2025</v>
       </c>
       <c r="E40">
-        <v>191160</v>
+        <v>143960</v>
       </c>
       <c r="F40">
-        <v>162000</v>
+        <v>122000</v>
       </c>
       <c r="G40">
-        <v>29160</v>
+        <v>21960</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>2025-11</v>
       </c>
       <c r="L40" t="str">
-        <v>12/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="M40" t="str">
         <v>Yes</v>
@@ -2115,19 +2115,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C41" t="str">
-        <v>S24/2025/011</v>
+        <v>S24/2025/012</v>
       </c>
       <c r="D41" t="str">
-        <v>02/10/2025</v>
+        <v>06/10/2025</v>
       </c>
       <c r="E41">
-        <v>156940</v>
+        <v>148680</v>
       </c>
       <c r="F41">
-        <v>133000</v>
+        <v>126000</v>
       </c>
       <c r="G41">
-        <v>23940</v>
+        <v>22680</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>2025-11</v>
       </c>
       <c r="L41" t="str">
-        <v>14/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M41" t="str">
         <v>Yes</v>
@@ -2162,19 +2162,19 @@
         <v>Yamuna Agro Products</v>
       </c>
       <c r="C42" t="str">
-        <v>S24/2025/012</v>
+        <v>S24/2025/013</v>
       </c>
       <c r="D42" t="str">
         <v>19/10/2025</v>
       </c>
       <c r="E42">
-        <v>168740</v>
+        <v>169920</v>
       </c>
       <c r="F42">
-        <v>143000</v>
+        <v>144000</v>
       </c>
       <c r="G42">
-        <v>25740</v>
+        <v>25920</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>2025-11</v>
       </c>
       <c r="L42" t="str">
-        <v>11/11/2025</v>
+        <v>09/11/2025</v>
       </c>
       <c r="M42" t="str">
         <v>Yes</v>
@@ -2203,31 +2203,31 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09AAJFY5523C1Z3</v>
+        <v>27AABCZ9934D1Z1</v>
       </c>
       <c r="B43" t="str">
-        <v>Yamuna Agro Products</v>
+        <v>Zenith Tooling</v>
       </c>
       <c r="C43" t="str">
-        <v>S24/2025/013</v>
+        <v>S25/2025/011</v>
       </c>
       <c r="D43" t="str">
-        <v>02/10/2025</v>
+        <v>24/10/2025</v>
       </c>
       <c r="E43">
-        <v>143960</v>
+        <v>55460</v>
       </c>
       <c r="F43">
-        <v>122000</v>
+        <v>47000</v>
       </c>
       <c r="G43">
-        <v>21960</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2236,7 +2236,7 @@
         <v>2025-11</v>
       </c>
       <c r="L43" t="str">
-        <v>16/11/2025</v>
+        <v>13/11/2025</v>
       </c>
       <c r="M43" t="str">
         <v>Yes</v>
@@ -2245,59 +2245,12 @@
         <v/>
       </c>
       <c r="O43" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>27AABCZ9934D1Z1</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Zenith Tooling</v>
-      </c>
-      <c r="C44" t="str">
-        <v>S25/2025/011</v>
-      </c>
-      <c r="D44" t="str">
-        <v>07/10/2025</v>
-      </c>
-      <c r="E44">
-        <v>48380</v>
-      </c>
-      <c r="F44">
-        <v>41000</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>3690</v>
-      </c>
-      <c r="I44">
-        <v>3690</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="L44" t="str">
-        <v>12/11/2025</v>
-      </c>
-      <c r="M44" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
         <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O43"/>
   </ignoredErrors>
 </worksheet>
 </file>
